--- a/fake data/Doctor Schedule Calendar - T Groups.xlsx
+++ b/fake data/Doctor Schedule Calendar - T Groups.xlsx
@@ -2,129 +2,129 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doctor Directory" sheetId="1" r:id="R9947818666574a7f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D001" sheetId="2" r:id="R4f8bf819c0664cbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D002" sheetId="3" r:id="R86b169a239ba4390"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D003" sheetId="4" r:id="R252d9f014c9c48b1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D004" sheetId="5" r:id="R18896b33540549de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D005" sheetId="6" r:id="R0bde01d339274455"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D006" sheetId="7" r:id="R506fd80f15534225"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D007" sheetId="8" r:id="Rdab2bedbfd2443ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D008" sheetId="9" r:id="Rb6e515d3b7a2485e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D009" sheetId="10" r:id="R3143842b82bc4eda"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D010" sheetId="11" r:id="R5fab929040184355"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D011" sheetId="12" r:id="Re8f54d0e9c24462f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D012" sheetId="13" r:id="R8d728923c21a4896"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D013" sheetId="14" r:id="R7a61d66f47ba49e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D014" sheetId="15" r:id="R786b12e652c341cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D015" sheetId="16" r:id="Rf08864dcf21e4a8a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D016" sheetId="17" r:id="Rf244394309d04e66"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D017" sheetId="18" r:id="Rc451295abd2b447c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D018" sheetId="19" r:id="R1b9c364935914754"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D019" sheetId="20" r:id="R73363094adfc4fd8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D020" sheetId="21" r:id="R29d92f511462493d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D021" sheetId="22" r:id="R7ae5386ee8cf4a86"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D022" sheetId="23" r:id="R0abb2a2a86f24e1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D023" sheetId="24" r:id="R89e3d7cbe8eb4f33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D024" sheetId="25" r:id="Re01c3cc51f8e42b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D025" sheetId="26" r:id="R688aad9df11a48a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D026" sheetId="27" r:id="Re263c455d58b44b5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D027" sheetId="28" r:id="Ref112d36430e45be"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D028" sheetId="29" r:id="Rd916352c3a774e7b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D029" sheetId="30" r:id="Rf8e21b701aa14cad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D030" sheetId="31" r:id="Rdb679ad5bf4d43ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D031" sheetId="32" r:id="Rd365827fa28e4301"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D032" sheetId="33" r:id="Rf957474a070a429b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D033" sheetId="34" r:id="R6bf954d1d4114d80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D034" sheetId="35" r:id="R8df4299167a2462b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D035" sheetId="36" r:id="R28b591a54c8e46ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D036" sheetId="37" r:id="Rd7f1c465759d4bbe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D037" sheetId="38" r:id="R8a12c411bdc646fb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D038" sheetId="39" r:id="Rce105a8128114db4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D039" sheetId="40" r:id="R2be783a2ca5a4220"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D040" sheetId="41" r:id="Ra3e0649bb6c440ec"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D041" sheetId="42" r:id="R92f2a573f97f4e85"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D042" sheetId="43" r:id="R90e9be8bade84da6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D043" sheetId="44" r:id="R2a4ea80cba9c4781"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D044" sheetId="45" r:id="R41c188c2d94b4a6f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D045" sheetId="46" r:id="R2f9aac9be8464fd2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D046" sheetId="47" r:id="Rfdd6f9c23a424092"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D047" sheetId="48" r:id="Rf0d2c7e4a28548ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D048" sheetId="49" r:id="Rcc8512e07c4b417a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D049" sheetId="50" r:id="R156b504270ca4f2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D050" sheetId="51" r:id="R46fc7da84fe148ea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D051" sheetId="52" r:id="R764706bdc27046d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D052" sheetId="53" r:id="R1a31b7550cce4da3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D053" sheetId="54" r:id="Rcf5f72ec11a444ac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D054" sheetId="55" r:id="Rcc84defdce484ca2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D055" sheetId="56" r:id="Rdd9218f1ae2c45d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D056" sheetId="57" r:id="Rb9664951a9ed4a93"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D057" sheetId="58" r:id="R8add9d603e97497c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D058" sheetId="59" r:id="R7a7636fc43e64631"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D059" sheetId="60" r:id="R4f77a21249274f18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D060" sheetId="61" r:id="R79e7783caebb4ce0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D061" sheetId="62" r:id="Rbded892680c44267"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D062" sheetId="63" r:id="Refea743956ba4c89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D063" sheetId="64" r:id="R5e2e58e1880749c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D064" sheetId="65" r:id="R5378973e90484bc5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D065" sheetId="66" r:id="Rab313b92994d45ce"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D066" sheetId="67" r:id="Rdc4e3b0a49614c26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D067" sheetId="68" r:id="R39b4d1a526e74bbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D068" sheetId="69" r:id="R4107fecf6b1c4144"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D069" sheetId="70" r:id="Rd7cb7b0f8d7446a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D070" sheetId="71" r:id="Rf3483995fb1a4f39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D071" sheetId="72" r:id="R8c04d1d115944db3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D072" sheetId="73" r:id="R8c9b64e19e344dbd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D073" sheetId="74" r:id="R52ef05ae31f8492b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D074" sheetId="75" r:id="R9e3f1b2193a1454d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D075" sheetId="76" r:id="R93a3f9edfb4b4508"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D076" sheetId="77" r:id="R3a65c54562ba4a3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D077" sheetId="78" r:id="R0e7a6a26244c4b9e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D078" sheetId="79" r:id="Ra007ab6c88d04756"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D079" sheetId="80" r:id="R2cc119c820d64aa9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D080" sheetId="81" r:id="R1173bea942e3490a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D081" sheetId="82" r:id="R0a961c54087e43d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D082" sheetId="83" r:id="R773003c0b866428f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D083" sheetId="84" r:id="R2a9bd93a0c674da8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D084" sheetId="85" r:id="R05db58c8611e42a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D085" sheetId="86" r:id="R96c974191f794a83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D086" sheetId="87" r:id="Ra3d8e40265bf42aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D087" sheetId="88" r:id="R8b9f6ae5e65e4147"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D088" sheetId="89" r:id="R9efe0b976f874de1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D089" sheetId="90" r:id="R369717b61e314b0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D090" sheetId="91" r:id="R3c2617b3b506471c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D091" sheetId="92" r:id="Rd596c1a034084977"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D092" sheetId="93" r:id="R616a6ce589924a75"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D093" sheetId="94" r:id="R6c37455058384155"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D094" sheetId="95" r:id="Raa2452255e0d454c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D095" sheetId="96" r:id="Rcfbf42223b4a4b0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D096" sheetId="97" r:id="Rab3ca01876dd4fbc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D097" sheetId="98" r:id="R0f084ec5262046e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D098" sheetId="99" r:id="R2f77916981f84539"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D099" sheetId="100" r:id="Red809fc9b8bc4ef8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D100" sheetId="101" r:id="R992c9140132642c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D101" sheetId="102" r:id="R0799f7d4526e4697"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D102" sheetId="103" r:id="R4af4d012d81c42dc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D103" sheetId="104" r:id="R9f757339a0bf4d02"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D104" sheetId="105" r:id="R66c27e6a531a411d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D105" sheetId="106" r:id="R445d090813944a29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D106" sheetId="107" r:id="R592805d9d4d34546"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D107" sheetId="108" r:id="R8ebbc2fde4724632"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D108" sheetId="109" r:id="Rb72a87c4c10b4e7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D109" sheetId="110" r:id="R1bd53c1a214345d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D110" sheetId="111" r:id="R904b63f853d94dd1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D111" sheetId="112" r:id="Ra267da95ef4544f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D112" sheetId="113" r:id="Rc9ccc1b1c0cc47cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D113" sheetId="114" r:id="R5d19454186004746"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D114" sheetId="115" r:id="R74299464bc2145c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D115" sheetId="116" r:id="R42271bd93a5a4b00"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D116" sheetId="117" r:id="R5c00268080ba4b25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D117" sheetId="118" r:id="Rf5d3acd7fdca4392"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D118" sheetId="119" r:id="Re21467dd830b4755"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D119" sheetId="120" r:id="Rf3541e882cc1457a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D120" sheetId="121" r:id="R9603802c65694112"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D121" sheetId="122" r:id="R9c19c6b7ee3343cf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D122" sheetId="123" r:id="R61f976bfd81548a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Doctor Directory" sheetId="1" r:id="Rc61c5b1f25e44f6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D001" sheetId="2" r:id="R9ab76a7ede124483"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D002" sheetId="3" r:id="R3d26224365404a9b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D003" sheetId="4" r:id="Rd9fe44469f944bc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D004" sheetId="5" r:id="R77b0dd2213514530"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D005" sheetId="6" r:id="R497cb4d570b1404e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D006" sheetId="7" r:id="R4a6236b936f14a20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D007" sheetId="8" r:id="R666d0ab800224238"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D008" sheetId="9" r:id="R7d5ea2b599a648b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D009" sheetId="10" r:id="R796bd23365d94bf9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D010" sheetId="11" r:id="R44191db22b4f43f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D011" sheetId="12" r:id="R15981bf01edd433e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D012" sheetId="13" r:id="R7e528fd382ff42b5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D013" sheetId="14" r:id="Rbbd86f01b6a549e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D014" sheetId="15" r:id="R24155c9b42da4df6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D015" sheetId="16" r:id="R2f16e216f3ab4313"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D016" sheetId="17" r:id="R2852ab79dedf4864"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D017" sheetId="18" r:id="R157259ff52e340a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D018" sheetId="19" r:id="R63c1661615154623"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D019" sheetId="20" r:id="Rdc193b6756d4459b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D020" sheetId="21" r:id="Re5acc2073b964259"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D021" sheetId="22" r:id="R7ecda4eec5db4218"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D022" sheetId="23" r:id="Rba01d8adfc494284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D023" sheetId="24" r:id="R10d6f69a2c1a4746"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D024" sheetId="25" r:id="R42f28cc595664d3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D025" sheetId="26" r:id="R5b83856105d14c57"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D026" sheetId="27" r:id="R26aac3961cc84886"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D027" sheetId="28" r:id="Rb46f6eca791e47b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D028" sheetId="29" r:id="R37255e18e1da4f76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D029" sheetId="30" r:id="Ra749fca1018a400a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D030" sheetId="31" r:id="R06002ba2ec164347"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D031" sheetId="32" r:id="R3227acd3955943e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D032" sheetId="33" r:id="R495715da4cf74c1b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D033" sheetId="34" r:id="R647e2aecb4f14030"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D034" sheetId="35" r:id="Rc90b7eaf52c74552"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D035" sheetId="36" r:id="R78bfdb6f6bba4524"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D036" sheetId="37" r:id="R2529b4e8de5742e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D037" sheetId="38" r:id="R9db79aed8afd460d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D038" sheetId="39" r:id="Rc525eed724d640b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D039" sheetId="40" r:id="Rf600506e189a4d6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D040" sheetId="41" r:id="Ree249d097b4448a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D041" sheetId="42" r:id="R63e012071173428c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D042" sheetId="43" r:id="R12b519e8fc164374"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D043" sheetId="44" r:id="R718e045c108d4e86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D044" sheetId="45" r:id="R14fe8955ea594ce5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D045" sheetId="46" r:id="R6746fc2731984c21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D046" sheetId="47" r:id="Rdb812c60a4ba44a6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D047" sheetId="48" r:id="R8e391f2a61a74f31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D048" sheetId="49" r:id="Rdb2a70aab1b94670"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D049" sheetId="50" r:id="Rf86fee236b8241b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D050" sheetId="51" r:id="R48f7233c5f3049ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D051" sheetId="52" r:id="R721c5d8523544464"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D052" sheetId="53" r:id="Rc00e686246534674"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D053" sheetId="54" r:id="R388e7914df404c48"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D054" sheetId="55" r:id="R4e426a2875274c14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D055" sheetId="56" r:id="Rb14fa2a42ba542b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D056" sheetId="57" r:id="Re63f5e92714b4ed0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D057" sheetId="58" r:id="R0414c9ed2c944a8a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D058" sheetId="59" r:id="Rbc96c84e19744790"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D059" sheetId="60" r:id="R2b15a134f9824037"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D060" sheetId="61" r:id="Rda31def6ca394f50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D061" sheetId="62" r:id="R901c82eeddd94dc9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D062" sheetId="63" r:id="R41145f228a51442c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D063" sheetId="64" r:id="R5b7db3f9247241af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D064" sheetId="65" r:id="R07be8f1be4884c9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D065" sheetId="66" r:id="R0100ea70aa58499d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D066" sheetId="67" r:id="R5d7275b5b8f54abe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D067" sheetId="68" r:id="Rac2ddb600fd24986"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D068" sheetId="69" r:id="R6746f42db4a24fc8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D069" sheetId="70" r:id="Ra86a408b6d6a44c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D070" sheetId="71" r:id="R87d69375b0334486"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D071" sheetId="72" r:id="R2d1cba9293514eba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D072" sheetId="73" r:id="Re5e903343e694d86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D073" sheetId="74" r:id="R8b6daee9fb5a4c76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D074" sheetId="75" r:id="Rb699b3fb609841fc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D075" sheetId="76" r:id="Ree85ff0798614e47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D076" sheetId="77" r:id="Rcd8e419064f2489e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D077" sheetId="78" r:id="Raea699b5a9ad44c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D078" sheetId="79" r:id="R074cc09c03a94ba4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D079" sheetId="80" r:id="R62c062cfd85d481e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D080" sheetId="81" r:id="R7a554776f9224ee5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D081" sheetId="82" r:id="Rf93091e83bd748a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D082" sheetId="83" r:id="R48a9171503c64b2f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D083" sheetId="84" r:id="R2edc1f7e08924c7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D084" sheetId="85" r:id="R10165f929f594cd9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D085" sheetId="86" r:id="R4cf84ea6c184469b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D086" sheetId="87" r:id="Rb0b3d247c7d4492b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D087" sheetId="88" r:id="R185a9ba1fbd440f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D088" sheetId="89" r:id="R836b1a6dbcfa4340"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D089" sheetId="90" r:id="Ra8d235aa33bd4b8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D090" sheetId="91" r:id="Rb7fb41a086b24701"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D091" sheetId="92" r:id="Rb14db50bdefd4e87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D092" sheetId="93" r:id="Re348bfe9402f4a64"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D093" sheetId="94" r:id="R5ce619d8b96d40e2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D094" sheetId="95" r:id="R3f8bc1479f6e42fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D095" sheetId="96" r:id="R556e85b5d449427b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D096" sheetId="97" r:id="Rba0f439d61d54a49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D097" sheetId="98" r:id="R04a113c8a9ad4604"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D098" sheetId="99" r:id="Rb7de09401e444067"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D099" sheetId="100" r:id="Ra9c56cbca0874883"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D100" sheetId="101" r:id="R9b100e860abc4869"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D101" sheetId="102" r:id="Rd495793bdad8409e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D102" sheetId="103" r:id="Rdef61874e9d140d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D103" sheetId="104" r:id="R9d93081e1b0e4a4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D104" sheetId="105" r:id="R3d1912b23a8947a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D105" sheetId="106" r:id="R561ad3b226e4411f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D106" sheetId="107" r:id="R8261743048594d34"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D107" sheetId="108" r:id="R9726705380174bdd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D108" sheetId="109" r:id="R070f2a5af0534a0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D109" sheetId="110" r:id="R378d59aae6ff44fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D110" sheetId="111" r:id="R55b246e027174261"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D111" sheetId="112" r:id="Rc9361a0a167d453b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D112" sheetId="113" r:id="R974b0e1c64634a0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D113" sheetId="114" r:id="R151bbc5282e64b1a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D114" sheetId="115" r:id="R608e0006e8aa4be1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D115" sheetId="116" r:id="R9b4ed41fe6b54224"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D116" sheetId="117" r:id="Rba7d45c722884da9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D117" sheetId="118" r:id="R41c8d99a9bef4387"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D118" sheetId="119" r:id="R3e839197a1c542e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D119" sheetId="120" r:id="R323951f1b05546f5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D120" sheetId="121" r:id="R126ab5deed5f4b86"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D121" sheetId="122" r:id="Rf75735fc079a43c0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="D122" sheetId="123" r:id="Rd76d786a7d5b4c7d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -693,7 +693,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R446cf1dcdc854139"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R59f7592bce604ead"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -3510,7 +3510,7 @@
     </x:row>
     <x:row r="2" ht="32" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>One weekly calendar tab per doctor, based on lecture assignments in the General Schedule. Tutorials and labs remain assigned to teaching assistants.</x:v>
+        <x:v>One weekly calendar per doctor, based on shared or major-specific lectures. Tutorials and labs are TA-led, single-major, and never shared across majors.</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -6822,9 +6822,9 @@
     <x:mergeCell ref="A2:P2"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8d3bb6e075384706"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8caa76ac84484b9e"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf514c6839acd44da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c6913567f3b4aa1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7122,7 +7122,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R39f2c65a31ec4477"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f3c7cfd29b54cd3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7465,7 +7465,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5931185200854dab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1a1319891cf643a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7808,7 +7808,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0eb9f7a2bbaf4fb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R356293c5abf44a5e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8151,7 +8151,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raf09aa2cc8444f39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56e8186e15b4499e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8539,7 +8539,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4770ab24995a414e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf26a2cae0bc643c0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8882,7 +8882,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6deb583ae706463c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c1955c82f6a457f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9270,7 +9270,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd30fe8e27afb4ac5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R677840a808ed4cda"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9703,7 +9703,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4ab5f68d50f546b7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R536dee62103240dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10001,7 +10001,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50f932b047b84115"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00ec476747734f9b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10389,7 +10389,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc415dcef5fff4002"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R247dbd9d36d648ff"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10957,7 +10957,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e573b9328904a55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R70a494e9bae5472c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11300,7 +11300,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf58f76168b1944bc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9307f280b3514d0e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11598,7 +11598,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f35d6d3191c4841"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1534585821b4e2d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12076,7 +12076,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07ff4313d1ab4ca0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbff4acf54bd24ae8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12374,7 +12374,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4cf6092013f46fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc568cac1f0fb4127"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12852,7 +12852,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f3f57ee64244166"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd24ae5941f9148a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13150,7 +13150,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cca422196d14649"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra86fc428dfca4639"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13718,7 +13718,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb4040d4731144b0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9145e6c44c42431a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14331,7 +14331,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf845f858a02344e4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5607fa8b0787440d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14899,7 +14899,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7703975253147b8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27dc7c1241264db5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15557,7 +15557,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24a38120c2bb4c62"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46ad30ece9f54440"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15855,7 +15855,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9445cf2ed2d4952"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f1c67eb43824986"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16243,7 +16243,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92b5d170cedc4902"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51afcb7ba7514b80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16676,7 +16676,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fa83cf0f4e549c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcaefd84e8e3041e2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17064,7 +17064,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb51bc6a4c9d349bf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R11b1d83cc6ef4c36"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17452,7 +17452,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd91b472eaf1d44d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa0d737129f64372"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17795,7 +17795,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rda317836cf7a4e11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b70066a53b24ff5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18363,7 +18363,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R098f38fe89e34800"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R504c79ae4387404a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18931,7 +18931,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1593fc2a13214972"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R13f7139b6ba5403a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19589,7 +19589,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf665a36ea08d4a90"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31cd93385bee4dbe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19887,7 +19887,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30d497e13d884a69"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R596efe7c6e82458a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20320,7 +20320,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4474b50cb39a4137"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red4ee44bff5a4397"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20663,7 +20663,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b88fd08423c4f5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R426ef55340a243be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21006,7 +21006,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19c04eaa614e4f9b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ree723a4be33f4df6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21439,7 +21439,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6cea3f4283724697"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a7518767aa14b9f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21872,7 +21872,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeb041a15a624561"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b5aa514baac48a5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22260,7 +22260,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5776d2905fde41f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71a9109c4c0d49d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -22648,7 +22648,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c2470bbd5194d45"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27e754b8124f46bb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23216,7 +23216,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab94b2f7b3c34056"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf43cb58fa804be5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23514,7 +23514,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0096822a7a484c14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c8feb3bb8624d6a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -23947,7 +23947,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re7f5c6745d5d4875"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R21abe96378ec4335"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24245,7 +24245,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcffe842b200498f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3b7a1da967ee460c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24678,7 +24678,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd522207a1664a2a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R19265f56545e423b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25156,7 +25156,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2e7bf29c80864fc9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45cdaf00e2194e46"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25499,7 +25499,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6b73c596d6a4375"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47427d24b5684624"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -25932,7 +25932,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R790befc4961d4409"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb0e9223308c431d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26320,7 +26320,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R921f054412e64bb0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R997a7dc4c2f7421d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26753,7 +26753,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e741cb4e5334470"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2959eeb0be844bdf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27141,7 +27141,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd4f0c896d9514525"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R277a539fd87b4a3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27529,7 +27529,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5985da38feca47df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5db2ac42ad7644cf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28007,7 +28007,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref5f475f96754648"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8cf036e784c84172"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28800,7 +28800,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a8d49947c0144b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c4330e6daaa4950"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29143,7 +29143,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d3ec5f11d614b28"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3c1ae0a991874799"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29576,7 +29576,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae7f57e09dc745a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R93ebead36fbc4616"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -29874,7 +29874,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0de07cad98084285"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f2adfda747b45e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30172,7 +30172,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9096bfe9e3b944ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf9a95c66f80d4b2f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30560,7 +30560,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4f1d2c444c94138"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cc12665ed2b4006"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -30993,7 +30993,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd8cf4fbe3ba4bda"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R350c5d7664e44578"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31471,7 +31471,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb11a9f460f734e2d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a47f88f6d3641fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -31949,7 +31949,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8bcc3a3c78264b29"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5fad4f0d4c0842a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32337,7 +32337,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d5232b9dfd44d62"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4753b9d5f304de5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -32770,7 +32770,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bb336c1972a4325"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R605fc9806cb34aa3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33563,7 +33563,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57baf9b7a6d24b70"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25ff764a96484ed0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -33951,7 +33951,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra9a6a377182f4dfa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca761c6a080e440c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -34429,7 +34429,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R43db4e4ced1d425c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06ba47f9c31642f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -34727,7 +34727,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a0849d3e29041c4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb94a81e22190485b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35250,7 +35250,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rabcf8b13b45b4425"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R623e8b0a5a90451a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -35683,7 +35683,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09e2302c6f2645c2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbdce50e7319d49ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36206,7 +36206,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00ce66955cac4fe2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb15849395a84476"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -36729,7 +36729,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58a8b4fce91f4020"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5cdeed5dd12b434d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37117,7 +37117,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbeed17663e5a41d9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49be458f6c7f446d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37505,7 +37505,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R391dfc3ff86941cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a7c565cc2474f7f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -37803,7 +37803,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1e4cccd7a10444c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff85181bf2724b58"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38281,7 +38281,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49d78a459183482f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9d635a09e275428e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -38714,7 +38714,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra8ac6c4f3855476a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra03a631951f64dea"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39327,7 +39327,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R50484fefbc384168"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32299c7cbeae4b4e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -39985,7 +39985,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc35d1a41d9e04d8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8eaa33e6dc234839"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40643,7 +40643,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R41c7813f47ed4868"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R602b69661a2a409d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -40986,7 +40986,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R07dc84920afa4e39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca13dff5307c486d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41599,7 +41599,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa8f62a985d44f7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdff66125f2f74b86"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -41987,7 +41987,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc753594644ea4d55"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0be4025ab50646a2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42285,7 +42285,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69389b72ea534cf6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89745b15e7d84378"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -42718,7 +42718,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R072d608cf9ac4123"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cf9020cb964414d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43151,7 +43151,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb21b2d17108d4516"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4f291511c174efb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43539,7 +43539,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R133c07a079bd4763"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9dc90aa40c1a4c45"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -43837,7 +43837,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ea970cf35c041af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77624baa56c6452f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44180,7 +44180,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc8d598b9da1144c5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R66642ca1a14542a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -44793,7 +44793,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R87e0f24c081b4b68"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R926ffecd8a52462e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45136,7 +45136,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf70a9ba646ad4318"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2cd43a866d84827"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -45704,7 +45704,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rada941f7ca3e4ca8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf77f50c6b5644021"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46002,7 +46002,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra74a5f47d7924aa5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f5b8343cb0542ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46300,7 +46300,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1c4e914bf974f09"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6a30cd1d376d4712"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46643,7 +46643,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R257f53835098410c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra21fd6de216243ac"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -46986,7 +46986,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91fb83144fca44d6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re51468cde0de471d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47509,7 +47509,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7394e69ba4524668"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc3037283358e4dc8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -47807,7 +47807,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re5c2f10bb19b493a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79c807e034a54e5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48195,7 +48195,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d6fd167e7de4487"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9352cf1860dc4382"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -48583,7 +48583,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49b407a0a8ab43b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbce128a597c84f53"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49016,7 +49016,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fa3a9a9d598460a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R346f9aaa69c1419e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49449,7 +49449,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f57b3a1b74d4b9a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7f8e1a7dfda4f3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -49882,7 +49882,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R771772d964694352"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde572eda5c05482f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -50720,7 +50720,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2bce0e234854a86"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1bfc9e93e04f4cc8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51108,7 +51108,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R54c1d5a6fd504844"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfbe1439414a84e1d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51541,7 +51541,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5edf3434bbcd4d1f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0d284375d1604fab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -51929,7 +51929,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2c57a8bc7b94caf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4ef269f48f349fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52317,7 +52317,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5024c7933f054faf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R04206c7fb80e4db3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -52615,7 +52615,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R97fec1d96de74d39"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7009255a5ae642ce"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53093,7 +53093,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8033fdf4aed4733"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rff47418c27ae468c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53391,7 +53391,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc63b2b24c1d84a8c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdae09f8547484599"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -53689,7 +53689,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5b3cc559faa048c8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re62142e36cba4c59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54077,7 +54077,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R76c1f4ba7316428c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R160b591bd7c94700"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54420,7 +54420,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95dccf42f25a4699"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R654ad04d28cd4d64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -54763,7 +54763,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61059828e2ec492d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcf3b0e1c88e64042"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -55196,7 +55196,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf965dc1491864f7a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R116094444d8642be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -55719,7 +55719,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49a3c93ffa0d4724"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc968e40b39274778"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -56107,7 +56107,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49f8c45de9444bf4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b27916a07ad4d90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -56405,7 +56405,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45a2986902c34592"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rea5d437c3339440f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -56793,7 +56793,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8428ec30fb29461a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf139debcb944a66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -57181,7 +57181,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5ba588f5b68d463c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0223d14e69844402"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -57614,7 +57614,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa23ce83b4984bcf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5a2e18410e074e3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -57912,7 +57912,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3735f5133c94d44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbb7f2f49b247442b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -58345,7 +58345,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7e8a02ccceef437c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R626358c69bec4d17"/>
   </x:tableParts>
 </x:worksheet>
 </file>